--- a/data/actual/clausura26.xlsx
+++ b/data/actual/clausura26.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E88B247-8659-4496-A3BD-4D5738A9FB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60045A22-C76C-4A8D-8567-5E6661A98585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="8" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fecha 1" sheetId="1" r:id="rId1"/>
     <sheet name="Fecha 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Fecha 3" sheetId="9" r:id="rId3"/>
-    <sheet name="Fecha 4" sheetId="8" r:id="rId4"/>
-    <sheet name="Fecha 5" sheetId="7" r:id="rId5"/>
-    <sheet name="Fecha 6" sheetId="5" r:id="rId6"/>
-    <sheet name="Fecha 7" sheetId="6" r:id="rId7"/>
-    <sheet name="Fecha 8" sheetId="3" r:id="rId8"/>
-    <sheet name="Fecha 9" sheetId="4" r:id="rId9"/>
+    <sheet name="Fecha 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Fecha 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Fecha 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Fecha 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Fecha 7" sheetId="7" r:id="rId7"/>
+    <sheet name="Fecha 8" sheetId="8" r:id="rId8"/>
+    <sheet name="Fecha 9" sheetId="9" r:id="rId9"/>
+    <sheet name="Fecha 10" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14101" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15679" uniqueCount="1162">
   <si>
     <t xml:space="preserve">  Club Atlético Belgrano  vs  Rosario Central</t>
   </si>
@@ -3330,6 +3331,201 @@
   </si>
   <si>
     <t>-1.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Central Córdoba  vs  Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>8/26 (31%)</t>
+  </si>
+  <si>
+    <t>10/27 (37%)</t>
+  </si>
+  <si>
+    <t>2.13</t>
+  </si>
+  <si>
+    <t>-0.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Racing Club  vs  Sarmiento</t>
+  </si>
+  <si>
+    <t>1.64</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>-2.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Gimnasia y Esgrima  vs  Banfield</t>
+  </si>
+  <si>
+    <t>3.54</t>
+  </si>
+  <si>
+    <t>10/20 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Gimnasia y Esgrima Mendoza  vs  Deportivo Riestra</t>
+  </si>
+  <si>
+    <t>14/19 (74%)</t>
+  </si>
+  <si>
+    <t>1/6 (17%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Club Atlético Unión de Santa Fe  vs  CA Independiente</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  River Plate  vs  Huracán</t>
+  </si>
+  <si>
+    <t>639</t>
+  </si>
+  <si>
+    <t>554</t>
+  </si>
+  <si>
+    <t>13/33 (39%)</t>
+  </si>
+  <si>
+    <t>-1.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instituto De Córdoba  vs  CA Talleres</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>2/2 (100%)</t>
+  </si>
+  <si>
+    <t>-1.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  San Lorenzo  vs  Boca Juniors</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>632</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>2.86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Club Atlético Platense  vs  Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>5/22 (23%)</t>
+  </si>
+  <si>
+    <t>2/11 (18%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Rosario Central  vs  Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>7/26 (27%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Club Atlético Belgrano  vs  Estudiantes de Río Cuarto</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Vélez Sarsfield  vs  Tigre</t>
+  </si>
+  <si>
+    <t>495</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>2.33</t>
+  </si>
+  <si>
+    <t>2.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Aldosivi  vs  Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Barracas Central  vs  Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>592</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>10/19 (53%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CA Lanús  vs  Estudiantes de La Plata</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>575</t>
+  </si>
+  <si>
+    <t>481</t>
+  </si>
+  <si>
+    <t>1.90</t>
+  </si>
+  <si>
+    <t>-0.10</t>
   </si>
 </sst>
 </file>
@@ -3414,21 +3610,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB0BEC5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB0BEC5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB0BEC5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB0BEC5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -3452,61 +3633,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0BEC5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0BEC5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0BEC5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0BEC5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3814,8 +4010,8 @@
   <dimension ref="A1:C672"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1">
@@ -4275,8 +4471,8 @@
       <c r="A46" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="3"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="2"/>
     </row>
     <row r="47" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A47" s="7" t="s">
@@ -4573,8 +4769,8 @@
       <c r="A74" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B74" s="2"/>
-      <c r="C74" s="3"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="2"/>
     </row>
     <row r="75" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A75" s="7" t="s">
@@ -4737,13 +4933,13 @@
       <c r="C90" s="16"/>
     </row>
     <row r="91" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B91" s="1">
-        <v>0</v>
-      </c>
-      <c r="C91" s="1">
+      <c r="B91" s="3">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3">
         <v>0</v>
       </c>
     </row>
@@ -4751,8 +4947,8 @@
       <c r="A92" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B92" s="2"/>
-      <c r="C92" s="3"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="2"/>
     </row>
     <row r="93" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A93" s="7" t="s">
@@ -5030,8 +5226,8 @@
       <c r="A119" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B119" s="2"/>
-      <c r="C119" s="3"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="2"/>
     </row>
     <row r="120" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A120" s="7" t="s">
@@ -5194,13 +5390,13 @@
     </row>
     <row r="135" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="136" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="1" t="s">
+      <c r="A136" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B136" s="1">
-        <v>0</v>
-      </c>
-      <c r="C136" s="1">
+      <c r="B136" s="3">
+        <v>0</v>
+      </c>
+      <c r="C136" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5208,8 +5404,8 @@
       <c r="A137" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B137" s="2"/>
-      <c r="C137" s="3"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="2"/>
     </row>
     <row r="138" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A138" s="7" t="s">
@@ -5487,8 +5683,8 @@
       <c r="A164" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B164" s="2"/>
-      <c r="C164" s="3"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="2"/>
     </row>
     <row r="165" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A165" s="7" t="s">
@@ -5643,13 +5839,13 @@
     <row r="179" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="180" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="181" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A181" s="1" t="s">
+      <c r="A181" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B181" s="1">
-        <v>0</v>
-      </c>
-      <c r="C181" s="1">
+      <c r="B181" s="3">
+        <v>0</v>
+      </c>
+      <c r="C181" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5657,8 +5853,8 @@
       <c r="A182" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B182" s="2"/>
-      <c r="C182" s="3"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="2"/>
     </row>
     <row r="183" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A183" s="7" t="s">
@@ -5936,8 +6132,8 @@
       <c r="A209" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B209" s="2"/>
-      <c r="C209" s="3"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="2"/>
     </row>
     <row r="210" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A210" s="7" t="s">
@@ -6092,13 +6288,13 @@
     <row r="224" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="225" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="226" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A226" s="1" t="s">
+      <c r="A226" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B226" s="1">
-        <v>0</v>
-      </c>
-      <c r="C226" s="1">
+      <c r="B226" s="3">
+        <v>0</v>
+      </c>
+      <c r="C226" s="3">
         <v>0</v>
       </c>
     </row>
@@ -6106,8 +6302,8 @@
       <c r="A227" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="B227" s="2"/>
-      <c r="C227" s="3"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="2"/>
     </row>
     <row r="228" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A228" s="7" t="s">
@@ -6385,8 +6581,8 @@
       <c r="A254" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B254" s="2"/>
-      <c r="C254" s="3"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="2"/>
     </row>
     <row r="255" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A255" s="7" t="s">
@@ -6541,13 +6737,13 @@
     <row r="269" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="270" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="271" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A271" s="1" t="s">
+      <c r="A271" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B271" s="1">
-        <v>0</v>
-      </c>
-      <c r="C271" s="1">
+      <c r="B271" s="3">
+        <v>0</v>
+      </c>
+      <c r="C271" s="3">
         <v>0</v>
       </c>
     </row>
@@ -6555,8 +6751,8 @@
       <c r="A272" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="B272" s="2"/>
-      <c r="C272" s="3"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="2"/>
     </row>
     <row r="273" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A273" s="7" t="s">
@@ -6834,8 +7030,8 @@
       <c r="A299" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B299" s="2"/>
-      <c r="C299" s="3"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="2"/>
     </row>
     <row r="300" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A300" s="7" t="s">
@@ -6990,13 +7186,13 @@
     <row r="314" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="315" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="316" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A316" s="1" t="s">
+      <c r="A316" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B316" s="1">
-        <v>0</v>
-      </c>
-      <c r="C316" s="1">
+      <c r="B316" s="3">
+        <v>0</v>
+      </c>
+      <c r="C316" s="3">
         <v>0</v>
       </c>
     </row>
@@ -7004,8 +7200,8 @@
       <c r="A317" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B317" s="2"/>
-      <c r="C317" s="3"/>
+      <c r="B317" s="1"/>
+      <c r="C317" s="2"/>
     </row>
     <row r="318" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A318" s="7" t="s">
@@ -7283,8 +7479,8 @@
       <c r="A344" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B344" s="2"/>
-      <c r="C344" s="3"/>
+      <c r="B344" s="1"/>
+      <c r="C344" s="2"/>
     </row>
     <row r="345" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A345" s="7" t="s">
@@ -7439,13 +7635,13 @@
     <row r="359" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="360" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="361" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A361" s="1" t="s">
+      <c r="A361" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B361" s="1">
-        <v>0</v>
-      </c>
-      <c r="C361" s="1">
+      <c r="B361" s="3">
+        <v>0</v>
+      </c>
+      <c r="C361" s="3">
         <v>0</v>
       </c>
     </row>
@@ -7453,8 +7649,8 @@
       <c r="A362" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="B362" s="2"/>
-      <c r="C362" s="3"/>
+      <c r="B362" s="1"/>
+      <c r="C362" s="2"/>
     </row>
     <row r="363" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A363" s="7" t="s">
@@ -7732,8 +7928,8 @@
       <c r="A389" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B389" s="2"/>
-      <c r="C389" s="3"/>
+      <c r="B389" s="1"/>
+      <c r="C389" s="2"/>
     </row>
     <row r="390" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A390" s="7" t="s">
@@ -7888,13 +8084,13 @@
     <row r="404" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="405" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="406" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A406" s="1" t="s">
+      <c r="A406" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B406" s="1">
-        <v>0</v>
-      </c>
-      <c r="C406" s="1">
+      <c r="B406" s="3">
+        <v>0</v>
+      </c>
+      <c r="C406" s="3">
         <v>0</v>
       </c>
     </row>
@@ -7902,8 +8098,8 @@
       <c r="A407" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="B407" s="2"/>
-      <c r="C407" s="3"/>
+      <c r="B407" s="1"/>
+      <c r="C407" s="2"/>
     </row>
     <row r="408" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A408" s="7" t="s">
@@ -8192,8 +8388,8 @@
       <c r="A435" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B435" s="2"/>
-      <c r="C435" s="3"/>
+      <c r="B435" s="1"/>
+      <c r="C435" s="2"/>
     </row>
     <row r="436" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A436" s="7" t="s">
@@ -8348,13 +8544,13 @@
     <row r="450" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="451" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="452" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A452" s="1" t="s">
+      <c r="A452" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B452" s="1">
-        <v>0</v>
-      </c>
-      <c r="C452" s="1">
+      <c r="B452" s="3">
+        <v>0</v>
+      </c>
+      <c r="C452" s="3">
         <v>0</v>
       </c>
     </row>
@@ -8362,8 +8558,8 @@
       <c r="A453" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B453" s="2"/>
-      <c r="C453" s="3"/>
+      <c r="B453" s="1"/>
+      <c r="C453" s="2"/>
     </row>
     <row r="454" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A454" s="7" t="s">
@@ -8641,8 +8837,8 @@
       <c r="A480" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B480" s="2"/>
-      <c r="C480" s="3"/>
+      <c r="B480" s="1"/>
+      <c r="C480" s="2"/>
     </row>
     <row r="481" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A481" s="7" t="s">
@@ -8797,13 +8993,13 @@
     <row r="495" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="496" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="497" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A497" s="1" t="s">
+      <c r="A497" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B497" s="1">
-        <v>0</v>
-      </c>
-      <c r="C497" s="1">
+      <c r="B497" s="3">
+        <v>0</v>
+      </c>
+      <c r="C497" s="3">
         <v>0</v>
       </c>
     </row>
@@ -8811,8 +9007,8 @@
       <c r="A498" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="B498" s="2"/>
-      <c r="C498" s="3"/>
+      <c r="B498" s="1"/>
+      <c r="C498" s="2"/>
     </row>
     <row r="499" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A499" s="7" t="s">
@@ -9090,8 +9286,8 @@
       <c r="A525" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B525" s="2"/>
-      <c r="C525" s="3"/>
+      <c r="B525" s="1"/>
+      <c r="C525" s="2"/>
     </row>
     <row r="526" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A526" s="7" t="s">
@@ -9246,13 +9442,13 @@
     <row r="540" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="541" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="542" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A542" s="1" t="s">
+      <c r="A542" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B542" s="1">
-        <v>0</v>
-      </c>
-      <c r="C542" s="1">
+      <c r="B542" s="3">
+        <v>0</v>
+      </c>
+      <c r="C542" s="3">
         <v>0</v>
       </c>
     </row>
@@ -9260,8 +9456,8 @@
       <c r="A543" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="B543" s="2"/>
-      <c r="C543" s="3"/>
+      <c r="B543" s="1"/>
+      <c r="C543" s="2"/>
     </row>
     <row r="544" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A544" s="7" t="s">
@@ -9517,8 +9713,8 @@
       <c r="A568" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B568" s="2"/>
-      <c r="C568" s="3"/>
+      <c r="B568" s="1"/>
+      <c r="C568" s="2"/>
     </row>
     <row r="569" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A569" s="7" t="s">
@@ -9673,13 +9869,13 @@
     <row r="583" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="584" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="585" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A585" s="1" t="s">
+      <c r="A585" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B585" s="1">
-        <v>0</v>
-      </c>
-      <c r="C585" s="1">
+      <c r="B585" s="3">
+        <v>0</v>
+      </c>
+      <c r="C585" s="3">
         <v>0</v>
       </c>
     </row>
@@ -9687,8 +9883,8 @@
       <c r="A586" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="B586" s="2"/>
-      <c r="C586" s="3"/>
+      <c r="B586" s="1"/>
+      <c r="C586" s="2"/>
     </row>
     <row r="587" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A587" s="7" t="s">
@@ -9966,8 +10162,8 @@
       <c r="A613" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B613" s="2"/>
-      <c r="C613" s="3"/>
+      <c r="B613" s="1"/>
+      <c r="C613" s="2"/>
     </row>
     <row r="614" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A614" s="7" t="s">
@@ -10122,13 +10318,13 @@
     <row r="628" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="629" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="630" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A630" s="1" t="s">
+      <c r="A630" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B630" s="1">
-        <v>0</v>
-      </c>
-      <c r="C630" s="1">
+      <c r="B630" s="3">
+        <v>0</v>
+      </c>
+      <c r="C630" s="3">
         <v>0</v>
       </c>
     </row>
@@ -10136,8 +10332,8 @@
       <c r="A631" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="B631" s="2"/>
-      <c r="C631" s="3"/>
+      <c r="B631" s="1"/>
+      <c r="C631" s="2"/>
     </row>
     <row r="632" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A632" s="7" t="s">
@@ -10404,8 +10600,8 @@
       <c r="A657" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B657" s="2"/>
-      <c r="C657" s="3"/>
+      <c r="B657" s="1"/>
+      <c r="C657" s="2"/>
     </row>
     <row r="658" spans="1:3">
       <c r="A658" s="7" t="s">
@@ -10562,13 +10758,13 @@
       </c>
     </row>
     <row r="672" spans="1:3">
-      <c r="A672" s="1" t="s">
+      <c r="A672" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B672" s="1">
-        <v>0</v>
-      </c>
-      <c r="C672" s="1">
+      <c r="B672" s="3">
+        <v>0</v>
+      </c>
+      <c r="C672" s="3">
         <v>0</v>
       </c>
     </row>
@@ -10581,7 +10777,7 @@
     <mergeCell ref="A398:C398"/>
     <mergeCell ref="A205:C205"/>
     <mergeCell ref="A617:C617"/>
-    <mergeCell ref="A249:C249"/>
+    <mergeCell ref="A293:C293"/>
     <mergeCell ref="A310:C310"/>
     <mergeCell ref="A337:C337"/>
     <mergeCell ref="A73:C73"/>
@@ -10593,7 +10789,7 @@
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A293:C293"/>
+    <mergeCell ref="A249:C249"/>
     <mergeCell ref="A354:C354"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A426:C426"/>
@@ -10609,13 +10805,6923 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:C674"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+    </row>
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>888</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="12">
+        <v>1</v>
+      </c>
+      <c r="C27" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="29" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A29" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+    </row>
+    <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="15">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="12">
+        <v>41.2</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A33" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="15">
+        <v>9.4E-2</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="12">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="15">
+        <v>0</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A36" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="12">
+        <v>0</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A37" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="15">
+        <v>0</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A38" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="12">
+        <v>0</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A39" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="15">
+        <v>0</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A40" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="12">
+        <v>0</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A41" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" s="15">
+        <v>-0.39</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A42" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="12">
+        <v>52.9</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A43" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="15">
+        <v>52.9</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="45" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="46" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+    </row>
+    <row r="47" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A47" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A48" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="8">
+        <v>3</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A49" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A50" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A51" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A52" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A53" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A54" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A55" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A56" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A57" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A58" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A59" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A60" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>961</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A61" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A62" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A63" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A64" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A65" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A66" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A67" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A68" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A69" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A70" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A71" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>871</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A72" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="12">
+        <v>0</v>
+      </c>
+      <c r="C72" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="74" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A74" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+    </row>
+    <row r="75" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A75" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A76" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B76" s="15">
+        <v>37.5</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A77" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="12">
+        <v>11.1</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A78" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="15">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A79" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="12">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A80" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="15">
+        <v>0</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A81" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B81" s="12">
+        <v>0</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A82" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" s="15">
+        <v>0</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A83" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B83" s="12">
+        <v>0</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A84" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B84" s="15">
+        <v>0</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A85" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B85" s="12">
+        <v>0</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A86" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B86" s="15">
+        <v>1.01</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A87" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B87" s="12">
+        <v>62.5</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A88" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B88" s="15">
+        <v>22.2</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="90" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="91" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A91" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16"/>
+    </row>
+    <row r="92" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A92" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A93" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93" s="8">
+        <v>2</v>
+      </c>
+      <c r="C93" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A94" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A95" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A96" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A97" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A99" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A100" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A101" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A102" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A103" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A104" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A105" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A106" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A107" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A108" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A109" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A110" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A111" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A112" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A113" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A114" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A115" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A116" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A117" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B117" s="12">
+        <v>1</v>
+      </c>
+      <c r="C117" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="119" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A119" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B119" s="16"/>
+      <c r="C119" s="16"/>
+    </row>
+    <row r="120" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A120" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A121" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B121" s="15">
+        <v>30.4</v>
+      </c>
+      <c r="C121" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A122" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B122" s="12">
+        <v>45.5</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A123" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B123" s="15">
+        <v>0.154</v>
+      </c>
+      <c r="C123" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A124" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B124" s="12">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A125" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B125" s="15">
+        <v>0</v>
+      </c>
+      <c r="C125" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A126" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B126" s="12">
+        <v>0</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A127" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B127" s="15">
+        <v>0</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A128" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B128" s="12">
+        <v>0</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A129" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B129" s="15">
+        <v>0</v>
+      </c>
+      <c r="C129" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A130" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B130" s="12">
+        <v>0</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A131" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B131" s="15">
+        <v>3.03</v>
+      </c>
+      <c r="C131" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A132" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B132" s="12">
+        <v>65.2</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A133" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B133" s="15">
+        <v>45.5</v>
+      </c>
+      <c r="C133" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="135" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="136" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A136" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B136" s="16"/>
+      <c r="C136" s="16"/>
+    </row>
+    <row r="137" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A137" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A138" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B138" s="8">
+        <v>0</v>
+      </c>
+      <c r="C138" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A139" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A140" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A141" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A142" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A144" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A145" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A146" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A147" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A148" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A149" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A150" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>756</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A151" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A152" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A153" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A154" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A155" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A156" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A157" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B157" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A158" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C158" s="12" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A159" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B159" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A160" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A161" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B161" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A162" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B162" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A163" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B163" s="10">
+        <v>0</v>
+      </c>
+      <c r="C163" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="165" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A165" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B165" s="16"/>
+      <c r="C165" s="16"/>
+    </row>
+    <row r="166" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A166" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A167" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B167" s="15">
+        <v>18.8</v>
+      </c>
+      <c r="C167" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A168" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B168" s="12">
+        <v>22.2</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A169" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B169" s="15">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="C169" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A170" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B170" s="12">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A171" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B171" s="15">
+        <v>0</v>
+      </c>
+      <c r="C171" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A172" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B172" s="12">
+        <v>0</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A173" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B173" s="15">
+        <v>0</v>
+      </c>
+      <c r="C173" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A174" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B174" s="12">
+        <v>0</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A175" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B175" s="15">
+        <v>0</v>
+      </c>
+      <c r="C175" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A176" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B176" s="12">
+        <v>0</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A177" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B177" s="15">
+        <v>0.41</v>
+      </c>
+      <c r="C177" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A178" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B178" s="12">
+        <v>56.2</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A179" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B179" s="15">
+        <v>66.7</v>
+      </c>
+      <c r="C179" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="181" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="182" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A182" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B182" s="16"/>
+      <c r="C182" s="16"/>
+    </row>
+    <row r="183" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A183" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A184" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B184" s="8">
+        <v>1</v>
+      </c>
+      <c r="C184" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A185" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C185" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A186" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A187" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A188" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C189" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A190" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A191" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C191" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A192" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A193" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A194" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A195" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A196" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A197" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B197" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C197" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A198" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B198" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A199" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A200" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B200" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A201" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A202" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A203" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="C203" s="10" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A204" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A205" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C205" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A206" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B206" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A207" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="C207" s="10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A208" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B208" s="12">
+        <v>0</v>
+      </c>
+      <c r="C208" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="210" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A210" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B210" s="16"/>
+      <c r="C210" s="16"/>
+    </row>
+    <row r="211" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A211" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A212" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B212" s="15">
+        <v>19</v>
+      </c>
+      <c r="C212" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A213" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B213" s="12">
+        <v>50</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A214" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B214" s="15">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="C214" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A215" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B215" s="12">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A216" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B216" s="15">
+        <v>0</v>
+      </c>
+      <c r="C216" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A217" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B217" s="12">
+        <v>0</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A218" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B218" s="15">
+        <v>0</v>
+      </c>
+      <c r="C218" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A219" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B219" s="12">
+        <v>0</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A220" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B220" s="15">
+        <v>0</v>
+      </c>
+      <c r="C220" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A221" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B221" s="12">
+        <v>0</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A222" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B222" s="15">
+        <v>1.17</v>
+      </c>
+      <c r="C222" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A223" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B223" s="12">
+        <v>66.7</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A224" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B224" s="15">
+        <v>50</v>
+      </c>
+      <c r="C224" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="226" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="227" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A227" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B227" s="16"/>
+      <c r="C227" s="16"/>
+    </row>
+    <row r="228" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A228" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A229" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B229" s="8">
+        <v>1</v>
+      </c>
+      <c r="C229" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A230" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C230" s="10" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A231" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B231" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A232" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C232" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A233" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C234" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A235" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B235" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A236" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C236" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A237" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B237" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A238" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C238" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A239" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B239" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A240" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C240" s="10" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A241" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B241" s="12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C241" s="12" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A242" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C242" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A243" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B243" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C243" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A244" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C244" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A245" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A246" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C246" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A247" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C247" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A248" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C248" s="10" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A249" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B249" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C249" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A250" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C250" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A251" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B251" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="C251" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A252" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A253" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B253" s="12">
+        <v>0</v>
+      </c>
+      <c r="C253" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="255" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A255" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B255" s="16"/>
+      <c r="C255" s="16"/>
+    </row>
+    <row r="256" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A256" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B256" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C256" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A257" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B257" s="15">
+        <v>15</v>
+      </c>
+      <c r="C257" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A258" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B258" s="12">
+        <v>28.6</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A259" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B259" s="15">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="C259" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A260" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B260" s="12">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="C260" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A261" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B261" s="15">
+        <v>0</v>
+      </c>
+      <c r="C261" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A262" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B262" s="12">
+        <v>0</v>
+      </c>
+      <c r="C262" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A263" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B263" s="15">
+        <v>0</v>
+      </c>
+      <c r="C263" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A264" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B264" s="12">
+        <v>0</v>
+      </c>
+      <c r="C264" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A265" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B265" s="15">
+        <v>0</v>
+      </c>
+      <c r="C265" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A266" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B266" s="12">
+        <v>0</v>
+      </c>
+      <c r="C266" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A267" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B267" s="15">
+        <v>1.39</v>
+      </c>
+      <c r="C267" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A268" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B268" s="12">
+        <v>60</v>
+      </c>
+      <c r="C268" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A269" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B269" s="15">
+        <v>0</v>
+      </c>
+      <c r="C269" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="271" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="272" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A272" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B272" s="16"/>
+      <c r="C272" s="16"/>
+    </row>
+    <row r="273" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A273" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B273" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A274" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B274" s="8">
+        <v>3</v>
+      </c>
+      <c r="C274" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A275" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B275" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C275" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A276" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="C276" s="12" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A277" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B277" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C277" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A278" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B278" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C278" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A279" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B279" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C279" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A280" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C280" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A281" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B281" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C281" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A282" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B282" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C282" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A283" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B283" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C283" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A284" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C284" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A285" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B285" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C285" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A286" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B286" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C286" s="12" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A287" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B287" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="C287" s="10" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A288" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B288" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C288" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A289" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B289" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C289" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A290" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C290" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A291" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B291" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C291" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A292" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C292" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A293" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B293" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C293" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A294" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C294" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A295" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B295" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C295" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A296" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B296" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C296" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A297" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B297" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C297" s="10" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A298" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B298" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="C298" s="12" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A299" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B299" s="10">
+        <v>0</v>
+      </c>
+      <c r="C299" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="301" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A301" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B301" s="16"/>
+      <c r="C301" s="16"/>
+    </row>
+    <row r="302" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A302" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C302" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A303" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B303" s="15">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="C303" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A304" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B304" s="12">
+        <v>16.7</v>
+      </c>
+      <c r="C304" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A305" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B305" s="15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="C305" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A306" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B306" s="12">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="C306" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A307" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B307" s="15">
+        <v>0</v>
+      </c>
+      <c r="C307" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A308" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B308" s="12">
+        <v>0</v>
+      </c>
+      <c r="C308" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A309" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B309" s="15">
+        <v>0</v>
+      </c>
+      <c r="C309" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A310" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B310" s="12">
+        <v>0</v>
+      </c>
+      <c r="C310" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A311" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B311" s="15">
+        <v>0</v>
+      </c>
+      <c r="C311" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A312" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B312" s="12">
+        <v>0</v>
+      </c>
+      <c r="C312" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A313" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B313" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="C313" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A314" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B314" s="12">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="C314" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A315" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B315" s="15">
+        <v>50</v>
+      </c>
+      <c r="C315" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="317" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="318" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A318" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B318" s="16"/>
+      <c r="C318" s="16"/>
+    </row>
+    <row r="319" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A319" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C319" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A320" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B320" s="8">
+        <v>0</v>
+      </c>
+      <c r="C320" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A321" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B321" s="10" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C321" s="10" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A322" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B322" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="C322" s="12" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A323" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B323" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C323" s="10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A324" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B324" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C324" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A325" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B325" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C325" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A326" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B326" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C326" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A327" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B327" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C327" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A328" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B328" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C328" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A329" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B329" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C329" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A330" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B330" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C330" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A331" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B331" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C331" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A332" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B332" s="12" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C332" s="12" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A333" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B333" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C333" s="10" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A334" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B334" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C334" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A335" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B335" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C335" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A336" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B336" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C336" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A337" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B337" s="10" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C337" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A338" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B338" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C338" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A339" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B339" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C339" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A340" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B340" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="C340" s="12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A341" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B341" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C341" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A342" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B342" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C342" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A343" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B343" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C343" s="10" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A344" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B344" s="12" t="s">
+        <v>623</v>
+      </c>
+      <c r="C344" s="12" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A345" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B345" s="10">
+        <v>0</v>
+      </c>
+      <c r="C345" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="347" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A347" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B347" s="16"/>
+      <c r="C347" s="16"/>
+    </row>
+    <row r="348" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A348" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B348" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C348" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A349" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B349" s="15">
+        <v>25</v>
+      </c>
+      <c r="C349" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A350" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B350" s="12">
+        <v>43.8</v>
+      </c>
+      <c r="C350" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A351" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B351" s="15">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="C351" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A352" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B352" s="12">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="C352" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A353" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B353" s="15">
+        <v>0</v>
+      </c>
+      <c r="C353" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A354" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B354" s="12">
+        <v>0</v>
+      </c>
+      <c r="C354" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A355" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B355" s="15">
+        <v>0</v>
+      </c>
+      <c r="C355" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A356" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B356" s="12">
+        <v>0</v>
+      </c>
+      <c r="C356" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A357" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B357" s="15">
+        <v>0</v>
+      </c>
+      <c r="C357" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A358" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B358" s="12">
+        <v>0</v>
+      </c>
+      <c r="C358" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A359" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B359" s="15">
+        <v>-1.94</v>
+      </c>
+      <c r="C359" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A360" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B360" s="12">
+        <v>50</v>
+      </c>
+      <c r="C360" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A361" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B361" s="15">
+        <v>68.8</v>
+      </c>
+      <c r="C361" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="363" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="364" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A364" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B364" s="16"/>
+      <c r="C364" s="16"/>
+    </row>
+    <row r="365" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A365" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C365" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A366" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B366" s="8">
+        <v>0</v>
+      </c>
+      <c r="C366" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A367" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B367" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C367" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A368" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B368" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C368" s="12" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A369" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B369" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C369" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A370" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B370" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C370" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A371" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B371" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C371" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A372" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B372" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C372" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A373" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B373" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C373" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A374" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B374" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C374" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A375" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B375" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C375" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A376" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B376" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C376" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A377" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B377" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C377" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A378" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="C378" s="12" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A379" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B379" s="10" t="s">
+        <v>962</v>
+      </c>
+      <c r="C379" s="10" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A380" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B380" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C380" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A381" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B381" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C381" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A382" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B382" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C382" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A383" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B383" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C383" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A384" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B384" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C384" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A385" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B385" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C385" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A386" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B386" s="12" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C386" s="12" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A387" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B387" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C387" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A388" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B388" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C388" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A389" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B389" s="10" t="s">
+        <v>960</v>
+      </c>
+      <c r="C389" s="10" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A390" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B390" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="C390" s="12" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A391" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B391" s="10">
+        <v>0</v>
+      </c>
+      <c r="C391" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="393" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A393" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B393" s="16"/>
+      <c r="C393" s="16"/>
+    </row>
+    <row r="394" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A394" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B394" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C394" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A395" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B395" s="15">
+        <v>40</v>
+      </c>
+      <c r="C395" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A396" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B396" s="12">
+        <v>44.4</v>
+      </c>
+      <c r="C396" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A397" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B397" s="15">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="C397" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A398" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B398" s="12">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="C398" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A399" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B399" s="15">
+        <v>0</v>
+      </c>
+      <c r="C399" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A400" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B400" s="12">
+        <v>0</v>
+      </c>
+      <c r="C400" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A401" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B401" s="15">
+        <v>0</v>
+      </c>
+      <c r="C401" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A402" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B402" s="12">
+        <v>0</v>
+      </c>
+      <c r="C402" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A403" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B403" s="15">
+        <v>0</v>
+      </c>
+      <c r="C403" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A404" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B404" s="12">
+        <v>0</v>
+      </c>
+      <c r="C404" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A405" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B405" s="15">
+        <v>-0.67</v>
+      </c>
+      <c r="C405" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A406" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B406" s="12">
+        <v>20</v>
+      </c>
+      <c r="C406" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A407" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B407" s="15">
+        <v>55.6</v>
+      </c>
+      <c r="C407" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="409" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="410" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A410" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B410" s="16"/>
+      <c r="C410" s="16"/>
+    </row>
+    <row r="411" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A411" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C411" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A412" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B412" s="8">
+        <v>1</v>
+      </c>
+      <c r="C412" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A413" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B413" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C413" s="10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A414" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B414" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="C414" s="12" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A415" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B415" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C415" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A416" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B416" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C416" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A417" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B417" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C417" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A418" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B418" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C418" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A419" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B419" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C419" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A420" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B420" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C420" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A421" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B421" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C421" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A422" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B422" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C422" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A423" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B423" s="10" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C423" s="10" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A424" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B424" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="C424" s="12" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A425" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B425" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C425" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A426" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B426" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C426" s="12" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A427" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B427" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C427" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A428" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B428" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C428" s="12" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A429" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B429" s="10" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C429" s="10" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A430" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B430" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C430" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A431" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B431" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C431" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A432" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B432" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="C432" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A433" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B433" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C433" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A434" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B434" s="12">
+        <v>0</v>
+      </c>
+      <c r="C434" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="436" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A436" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B436" s="16"/>
+      <c r="C436" s="16"/>
+    </row>
+    <row r="437" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A437" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B437" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C437" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A438" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B438" s="15">
+        <v>50</v>
+      </c>
+      <c r="C438" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A439" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B439" s="12">
+        <v>27.3</v>
+      </c>
+      <c r="C439" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A440" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B440" s="15">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="C440" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A441" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B441" s="12">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="C441" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A442" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B442" s="15">
+        <v>0</v>
+      </c>
+      <c r="C442" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A443" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B443" s="12">
+        <v>0</v>
+      </c>
+      <c r="C443" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A444" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B444" s="15">
+        <v>0</v>
+      </c>
+      <c r="C444" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A445" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B445" s="12">
+        <v>0</v>
+      </c>
+      <c r="C445" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A446" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B446" s="15">
+        <v>0</v>
+      </c>
+      <c r="C446" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A447" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B447" s="12">
+        <v>0</v>
+      </c>
+      <c r="C447" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A448" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B448" s="15">
+        <v>0.38</v>
+      </c>
+      <c r="C448" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A449" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B449" s="12">
+        <v>83.3</v>
+      </c>
+      <c r="C449" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A450" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B450" s="15">
+        <v>81.8</v>
+      </c>
+      <c r="C450" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="452" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="453" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A453" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B453" s="16"/>
+      <c r="C453" s="16"/>
+    </row>
+    <row r="454" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A454" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B454" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C454" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A455" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B455" s="8">
+        <v>2</v>
+      </c>
+      <c r="C455" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A456" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B456" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C456" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A457" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B457" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="C457" s="12" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A458" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B458" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C458" s="10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A459" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B459" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C459" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A460" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B460" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C460" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A461" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B461" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C461" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A462" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B462" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C462" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A463" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B463" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C463" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A464" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B464" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C464" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A465" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B465" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C465" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A466" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B466" s="10" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C466" s="10" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A467" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B467" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="C467" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A468" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B468" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C468" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A469" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B469" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C469" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A470" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B470" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C470" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A471" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B471" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="C471" s="12" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A472" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B472" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C472" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A473" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B473" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C473" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A474" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B474" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="C474" s="10" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A475" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B475" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C475" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A476" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B476" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C476" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A477" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B477" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="C477" s="12" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A478" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B478" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="C478" s="10" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A479" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B479" s="12">
+        <v>0</v>
+      </c>
+      <c r="C479" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="481" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A481" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B481" s="16"/>
+      <c r="C481" s="16"/>
+    </row>
+    <row r="482" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A482" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B482" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C482" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A483" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B483" s="15">
+        <v>40</v>
+      </c>
+      <c r="C483" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A484" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B484" s="12">
+        <v>31.2</v>
+      </c>
+      <c r="C484" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A485" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B485" s="15">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="C485" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A486" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B486" s="12">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="C486" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A487" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B487" s="15">
+        <v>0</v>
+      </c>
+      <c r="C487" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A488" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B488" s="12">
+        <v>0</v>
+      </c>
+      <c r="C488" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A489" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B489" s="15">
+        <v>0</v>
+      </c>
+      <c r="C489" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A490" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B490" s="12">
+        <v>0</v>
+      </c>
+      <c r="C490" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A491" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B491" s="15">
+        <v>0</v>
+      </c>
+      <c r="C491" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A492" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B492" s="12">
+        <v>0</v>
+      </c>
+      <c r="C492" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A493" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B493" s="15">
+        <v>-0.16</v>
+      </c>
+      <c r="C493" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A494" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B494" s="12">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="C494" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A495" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B495" s="15">
+        <v>68.8</v>
+      </c>
+      <c r="C495" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="497" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="498" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A498" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B498" s="16"/>
+      <c r="C498" s="16"/>
+    </row>
+    <row r="499" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A499" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B499" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C499" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A500" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B500" s="8">
+        <v>3</v>
+      </c>
+      <c r="C500" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A501" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B501" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C501" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A502" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B502" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="C502" s="12" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A503" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B503" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C503" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A504" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B504" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C504" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A505" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B505" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C505" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A506" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B506" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C506" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A507" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B507" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C507" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A508" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B508" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C508" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A509" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B509" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C509" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A510" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B510" s="12" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C510" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A511" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B511" s="10" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C511" s="10" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A512" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B512" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C512" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A513" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B513" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C513" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A514" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B514" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C514" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A515" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B515" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C515" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A516" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B516" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C516" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A517" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B517" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C517" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A518" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B518" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="C518" s="12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A519" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B519" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C519" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A520" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B520" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C520" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A521" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B521" s="10" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C521" s="10" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A522" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B522" s="12" t="s">
+        <v>910</v>
+      </c>
+      <c r="C522" s="12" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A523" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B523" s="10">
+        <v>0</v>
+      </c>
+      <c r="C523" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="525" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A525" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B525" s="16"/>
+      <c r="C525" s="16"/>
+    </row>
+    <row r="526" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A526" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B526" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C526" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A527" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B527" s="15">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="C527" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A528" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B528" s="12">
+        <v>69.2</v>
+      </c>
+      <c r="C528" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A529" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B529" s="15">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="C529" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A530" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B530" s="12">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="C530" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A531" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B531" s="15">
+        <v>0</v>
+      </c>
+      <c r="C531" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A532" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B532" s="12">
+        <v>0</v>
+      </c>
+      <c r="C532" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A533" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B533" s="15">
+        <v>0</v>
+      </c>
+      <c r="C533" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A534" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B534" s="12">
+        <v>0</v>
+      </c>
+      <c r="C534" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A535" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B535" s="15">
+        <v>0</v>
+      </c>
+      <c r="C535" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A536" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B536" s="12">
+        <v>0</v>
+      </c>
+      <c r="C536" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A537" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B537" s="15">
+        <v>-0.22</v>
+      </c>
+      <c r="C537" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A538" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B538" s="12">
+        <v>47.8</v>
+      </c>
+      <c r="C538" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A539" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B539" s="15">
+        <v>69.2</v>
+      </c>
+      <c r="C539" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="541" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="542" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A542" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B542" s="16"/>
+      <c r="C542" s="16"/>
+    </row>
+    <row r="543" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A543" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B543" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C543" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A544" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B544" s="8">
+        <v>1</v>
+      </c>
+      <c r="C544" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A545" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B545" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C545" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A546" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B546" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C546" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A547" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B547" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C547" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A548" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B548" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C548" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A549" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B549" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C549" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A550" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B550" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C550" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A551" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B551" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C551" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A552" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B552" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C552" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A553" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B553" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C553" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A554" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B554" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C554" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A555" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B555" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="C555" s="10" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A556" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B556" s="12" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C556" s="12" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A557" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B557" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C557" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A558" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B558" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C558" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A559" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B559" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C559" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A560" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B560" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C560" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A561" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B561" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C561" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A562" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B562" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C562" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A563" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B563" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C563" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A564" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B564" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C564" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A565" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B565" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C565" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A566" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B566" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C566" s="12" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A567" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B567" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C567" s="10" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A568" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B568" s="12">
+        <v>0</v>
+      </c>
+      <c r="C568" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="570" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A570" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B570" s="16"/>
+      <c r="C570" s="16"/>
+    </row>
+    <row r="571" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A571" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B571" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C571" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A572" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B572" s="15">
+        <v>23.1</v>
+      </c>
+      <c r="C572" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A573" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B573" s="12">
+        <v>7.7</v>
+      </c>
+      <c r="C573" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A574" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B574" s="15">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="C574" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A575" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B575" s="12">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="C575" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A576" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B576" s="15">
+        <v>0</v>
+      </c>
+      <c r="C576" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A577" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B577" s="12">
+        <v>0</v>
+      </c>
+      <c r="C577" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A578" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B578" s="15">
+        <v>0</v>
+      </c>
+      <c r="C578" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A579" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B579" s="12">
+        <v>0</v>
+      </c>
+      <c r="C579" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A580" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B580" s="15">
+        <v>0</v>
+      </c>
+      <c r="C580" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A581" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B581" s="12">
+        <v>0</v>
+      </c>
+      <c r="C581" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A582" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B582" s="15">
+        <v>0.39</v>
+      </c>
+      <c r="C582" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A583" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B583" s="12">
+        <v>61.5</v>
+      </c>
+      <c r="C583" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A584" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B584" s="15">
+        <v>53.8</v>
+      </c>
+      <c r="C584" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="586" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="587" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A587" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B587" s="16"/>
+      <c r="C587" s="16"/>
+    </row>
+    <row r="588" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A588" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B588" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C588" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A589" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B589" s="8">
+        <v>0</v>
+      </c>
+      <c r="C589" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A590" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B590" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C590" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A591" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B591" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C591" s="12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A592" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B592" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C592" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A593" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B593" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C593" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A594" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B594" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C594" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A595" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B595" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C595" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A596" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B596" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C596" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A597" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B597" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C597" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A598" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B598" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C598" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A599" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B599" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C599" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A600" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B600" s="10" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C600" s="10" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A601" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B601" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="C601" s="12" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A602" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B602" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C602" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A603" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B603" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C603" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A604" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B604" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C604" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A605" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B605" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C605" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A606" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B606" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C606" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A607" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B607" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C607" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A608" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B608" s="10" t="s">
+        <v>949</v>
+      </c>
+      <c r="C608" s="10" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A609" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B609" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C609" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A610" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B610" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C610" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A611" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B611" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="C611" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A612" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B612" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C612" s="10" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A613" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B613" s="12">
+        <v>0</v>
+      </c>
+      <c r="C613" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="615" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A615" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B615" s="16"/>
+      <c r="C615" s="16"/>
+    </row>
+    <row r="616" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A616" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B616" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C616" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A617" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B617" s="15">
+        <v>25</v>
+      </c>
+      <c r="C617" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A618" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B618" s="12">
+        <v>50</v>
+      </c>
+      <c r="C618" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A619" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B619" s="15">
+        <v>2.4E-2</v>
+      </c>
+      <c r="C619" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A620" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B620" s="12">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="C620" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A621" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B621" s="15">
+        <v>0</v>
+      </c>
+      <c r="C621" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A622" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B622" s="12">
+        <v>0</v>
+      </c>
+      <c r="C622" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A623" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B623" s="15">
+        <v>0</v>
+      </c>
+      <c r="C623" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A624" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B624" s="12">
+        <v>0</v>
+      </c>
+      <c r="C624" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A625" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B625" s="15">
+        <v>0</v>
+      </c>
+      <c r="C625" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A626" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B626" s="12">
+        <v>0</v>
+      </c>
+      <c r="C626" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A627" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B627" s="15">
+        <v>-0.92</v>
+      </c>
+      <c r="C627" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A628" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B628" s="12">
+        <v>25</v>
+      </c>
+      <c r="C628" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A629" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B629" s="15">
+        <v>50</v>
+      </c>
+      <c r="C629" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="631" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="632" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A632" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B632" s="16"/>
+      <c r="C632" s="16"/>
+    </row>
+    <row r="633" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A633" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B633" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C633" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A634" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B634" s="8">
+        <v>2</v>
+      </c>
+      <c r="C634" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A635" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B635" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C635" s="10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A636" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B636" s="12" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C636" s="12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A637" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B637" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C637" s="10" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A638" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B638" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C638" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A639" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B639" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C639" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A640" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B640" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C640" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A641" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B641" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C641" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A642" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B642" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C642" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A643" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B643" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C643" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A644" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B644" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C644" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A645" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B645" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="C645" s="10" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A646" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B646" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="C646" s="12" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A647" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B647" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C647" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A648" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B648" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C648" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A649" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B649" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C649" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A650" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B650" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C650" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A651" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B651" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C651" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A652" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B652" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C652" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A653" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B653" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="C653" s="10" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A654" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B654" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C654" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A655" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B655" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C655" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A656" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B656" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C656" s="12" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A657" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B657" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="C657" s="10" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A658" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B658" s="12">
+        <v>1</v>
+      </c>
+      <c r="C658" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="660" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A660" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B660" s="16"/>
+      <c r="C660" s="16"/>
+    </row>
+    <row r="661" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A661" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B661" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C661" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A662" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B662" s="15">
+        <v>50</v>
+      </c>
+      <c r="C662" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A663" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B663" s="12">
+        <v>20.8</v>
+      </c>
+      <c r="C663" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A664" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B664" s="15">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="C664" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A665" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B665" s="12">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="C665" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A666" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B666" s="15">
+        <v>0</v>
+      </c>
+      <c r="C666" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A667" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B667" s="12">
+        <v>0</v>
+      </c>
+      <c r="C667" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A668" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B668" s="15">
+        <v>0</v>
+      </c>
+      <c r="C668" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A669" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B669" s="12">
+        <v>0</v>
+      </c>
+      <c r="C669" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A670" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B670" s="15">
+        <v>0</v>
+      </c>
+      <c r="C670" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A671" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B671" s="12">
+        <v>0</v>
+      </c>
+      <c r="C671" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A672" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B672" s="15">
+        <v>-0.38</v>
+      </c>
+      <c r="C672" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A673" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B673" s="12">
+        <v>66.7</v>
+      </c>
+      <c r="C673" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A674" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B674" s="15">
+        <v>54.2</v>
+      </c>
+      <c r="C674" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A632:C632"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A570:C570"/>
+    <mergeCell ref="A227:C227"/>
+    <mergeCell ref="A498:C498"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A660:C660"/>
+    <mergeCell ref="A436:C436"/>
+    <mergeCell ref="A318:C318"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A525:C525"/>
+    <mergeCell ref="A481:C481"/>
+    <mergeCell ref="A347:C347"/>
+    <mergeCell ref="A182:C182"/>
+    <mergeCell ref="A615:C615"/>
+    <mergeCell ref="A587:C587"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A301:C301"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A210:C210"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A542:C542"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A453:C453"/>
+    <mergeCell ref="A364:C364"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A91:C91"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C672"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1">
@@ -11075,8 +18181,8 @@
       <c r="A46" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="3"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="2"/>
     </row>
     <row r="47" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A47" s="7" t="s">
@@ -11362,8 +18468,8 @@
       <c r="A73" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="3"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="2"/>
     </row>
     <row r="74" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A74" s="7" t="s">
@@ -11526,13 +18632,13 @@
       <c r="C89" s="16"/>
     </row>
     <row r="90" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B90" s="1">
-        <v>0</v>
-      </c>
-      <c r="C90" s="1">
+      <c r="B90" s="3">
+        <v>0</v>
+      </c>
+      <c r="C90" s="3">
         <v>0</v>
       </c>
     </row>
@@ -11540,8 +18646,8 @@
       <c r="A91" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="B91" s="2"/>
-      <c r="C91" s="3"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="2"/>
     </row>
     <row r="92" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="7" t="s">
@@ -11819,8 +18925,8 @@
       <c r="A118" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B118" s="2"/>
-      <c r="C118" s="3"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="2"/>
     </row>
     <row r="119" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A119" s="7" t="s">
@@ -11983,13 +19089,13 @@
     </row>
     <row r="134" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="135" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="1" t="s">
+      <c r="A135" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B135" s="1">
-        <v>0</v>
-      </c>
-      <c r="C135" s="1">
+      <c r="B135" s="3">
+        <v>0</v>
+      </c>
+      <c r="C135" s="3">
         <v>0</v>
       </c>
     </row>
@@ -11997,8 +19103,8 @@
       <c r="A136" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="B136" s="2"/>
-      <c r="C136" s="3"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="2"/>
     </row>
     <row r="137" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A137" s="7" t="s">
@@ -12276,8 +19382,8 @@
       <c r="A163" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B163" s="2"/>
-      <c r="C163" s="3"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="2"/>
     </row>
     <row r="164" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A164" s="7" t="s">
@@ -12432,13 +19538,13 @@
     <row r="178" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="179" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="180" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A180" s="1" t="s">
+      <c r="A180" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B180" s="1">
-        <v>0</v>
-      </c>
-      <c r="C180" s="1">
+      <c r="B180" s="3">
+        <v>0</v>
+      </c>
+      <c r="C180" s="3">
         <v>0</v>
       </c>
     </row>
@@ -12446,8 +19552,8 @@
       <c r="A181" s="17" t="s">
         <v>340</v>
       </c>
-      <c r="B181" s="2"/>
-      <c r="C181" s="3"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="2"/>
     </row>
     <row r="182" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A182" s="7" t="s">
@@ -12725,8 +19831,8 @@
       <c r="A208" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B208" s="2"/>
-      <c r="C208" s="3"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="2"/>
     </row>
     <row r="209" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A209" s="7" t="s">
@@ -12881,13 +19987,13 @@
     <row r="223" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="224" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="225" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A225" s="1" t="s">
+      <c r="A225" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B225" s="1">
-        <v>0</v>
-      </c>
-      <c r="C225" s="1">
+      <c r="B225" s="3">
+        <v>0</v>
+      </c>
+      <c r="C225" s="3">
         <v>0</v>
       </c>
     </row>
@@ -12895,8 +20001,8 @@
       <c r="A226" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="B226" s="2"/>
-      <c r="C226" s="3"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="2"/>
     </row>
     <row r="227" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A227" s="7" t="s">
@@ -13174,8 +20280,8 @@
       <c r="A253" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B253" s="2"/>
-      <c r="C253" s="3"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="2"/>
     </row>
     <row r="254" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A254" s="7" t="s">
@@ -13330,13 +20436,13 @@
     <row r="268" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="269" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="270" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A270" s="1" t="s">
+      <c r="A270" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B270" s="1">
-        <v>0</v>
-      </c>
-      <c r="C270" s="1">
+      <c r="B270" s="3">
+        <v>0</v>
+      </c>
+      <c r="C270" s="3">
         <v>0</v>
       </c>
     </row>
@@ -13344,8 +20450,8 @@
       <c r="A271" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="B271" s="2"/>
-      <c r="C271" s="3"/>
+      <c r="B271" s="1"/>
+      <c r="C271" s="2"/>
     </row>
     <row r="272" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A272" s="7" t="s">
@@ -13623,8 +20729,8 @@
       <c r="A298" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B298" s="2"/>
-      <c r="C298" s="3"/>
+      <c r="B298" s="1"/>
+      <c r="C298" s="2"/>
     </row>
     <row r="299" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A299" s="7" t="s">
@@ -13779,13 +20885,13 @@
     <row r="313" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="314" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="315" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A315" s="1" t="s">
+      <c r="A315" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B315" s="1">
-        <v>0</v>
-      </c>
-      <c r="C315" s="1">
+      <c r="B315" s="3">
+        <v>0</v>
+      </c>
+      <c r="C315" s="3">
         <v>0</v>
       </c>
     </row>
@@ -13793,8 +20899,8 @@
       <c r="A316" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="B316" s="2"/>
-      <c r="C316" s="3"/>
+      <c r="B316" s="1"/>
+      <c r="C316" s="2"/>
     </row>
     <row r="317" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A317" s="7" t="s">
@@ -14072,8 +21178,8 @@
       <c r="A343" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B343" s="2"/>
-      <c r="C343" s="3"/>
+      <c r="B343" s="1"/>
+      <c r="C343" s="2"/>
     </row>
     <row r="344" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A344" s="7" t="s">
@@ -14228,13 +21334,13 @@
     <row r="358" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="359" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="360" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A360" s="1" t="s">
+      <c r="A360" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B360" s="1">
-        <v>0</v>
-      </c>
-      <c r="C360" s="1">
+      <c r="B360" s="3">
+        <v>0</v>
+      </c>
+      <c r="C360" s="3">
         <v>0</v>
       </c>
     </row>
@@ -14242,8 +21348,8 @@
       <c r="A361" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="B361" s="2"/>
-      <c r="C361" s="3"/>
+      <c r="B361" s="1"/>
+      <c r="C361" s="2"/>
     </row>
     <row r="362" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A362" s="7" t="s">
@@ -14521,8 +21627,8 @@
       <c r="A388" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B388" s="2"/>
-      <c r="C388" s="3"/>
+      <c r="B388" s="1"/>
+      <c r="C388" s="2"/>
     </row>
     <row r="389" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A389" s="7" t="s">
@@ -14677,13 +21783,13 @@
     <row r="403" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="404" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="405" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A405" s="1" t="s">
+      <c r="A405" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B405" s="1">
-        <v>0</v>
-      </c>
-      <c r="C405" s="1">
+      <c r="B405" s="3">
+        <v>0</v>
+      </c>
+      <c r="C405" s="3">
         <v>0</v>
       </c>
     </row>
@@ -14691,8 +21797,8 @@
       <c r="A406" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="B406" s="2"/>
-      <c r="C406" s="3"/>
+      <c r="B406" s="1"/>
+      <c r="C406" s="2"/>
     </row>
     <row r="407" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A407" s="7" t="s">
@@ -14970,8 +22076,8 @@
       <c r="A433" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B433" s="2"/>
-      <c r="C433" s="3"/>
+      <c r="B433" s="1"/>
+      <c r="C433" s="2"/>
     </row>
     <row r="434" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A434" s="7" t="s">
@@ -15126,13 +22232,13 @@
     <row r="448" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="449" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="450" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A450" s="1" t="s">
+      <c r="A450" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B450" s="1">
-        <v>0</v>
-      </c>
-      <c r="C450" s="1">
+      <c r="B450" s="3">
+        <v>0</v>
+      </c>
+      <c r="C450" s="3">
         <v>0</v>
       </c>
     </row>
@@ -15140,8 +22246,8 @@
       <c r="A451" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="B451" s="2"/>
-      <c r="C451" s="3"/>
+      <c r="B451" s="1"/>
+      <c r="C451" s="2"/>
     </row>
     <row r="452" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A452" s="7" t="s">
@@ -15419,8 +22525,8 @@
       <c r="A478" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B478" s="2"/>
-      <c r="C478" s="3"/>
+      <c r="B478" s="1"/>
+      <c r="C478" s="2"/>
     </row>
     <row r="479" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A479" s="7" t="s">
@@ -15575,13 +22681,13 @@
     <row r="493" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="494" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="495" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A495" s="1" t="s">
+      <c r="A495" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B495" s="1">
-        <v>0</v>
-      </c>
-      <c r="C495" s="1">
+      <c r="B495" s="3">
+        <v>0</v>
+      </c>
+      <c r="C495" s="3">
         <v>0</v>
       </c>
     </row>
@@ -15589,8 +22695,8 @@
       <c r="A496" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="B496" s="2"/>
-      <c r="C496" s="3"/>
+      <c r="B496" s="1"/>
+      <c r="C496" s="2"/>
     </row>
     <row r="497" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A497" s="7" t="s">
@@ -15868,8 +22974,8 @@
       <c r="A523" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B523" s="2"/>
-      <c r="C523" s="3"/>
+      <c r="B523" s="1"/>
+      <c r="C523" s="2"/>
     </row>
     <row r="524" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A524" s="7" t="s">
@@ -16024,13 +23130,13 @@
     <row r="538" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="539" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="540" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A540" s="1" t="s">
+      <c r="A540" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B540" s="1">
-        <v>0</v>
-      </c>
-      <c r="C540" s="1">
+      <c r="B540" s="3">
+        <v>0</v>
+      </c>
+      <c r="C540" s="3">
         <v>0</v>
       </c>
     </row>
@@ -16038,8 +23144,8 @@
       <c r="A541" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="B541" s="2"/>
-      <c r="C541" s="3"/>
+      <c r="B541" s="1"/>
+      <c r="C541" s="2"/>
     </row>
     <row r="542" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A542" s="7" t="s">
@@ -16317,8 +23423,8 @@
       <c r="A568" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B568" s="2"/>
-      <c r="C568" s="3"/>
+      <c r="B568" s="1"/>
+      <c r="C568" s="2"/>
     </row>
     <row r="569" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A569" s="7" t="s">
@@ -16473,13 +23579,13 @@
     <row r="583" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="584" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="585" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A585" s="1" t="s">
+      <c r="A585" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B585" s="1">
-        <v>0</v>
-      </c>
-      <c r="C585" s="1">
+      <c r="B585" s="3">
+        <v>0</v>
+      </c>
+      <c r="C585" s="3">
         <v>0</v>
       </c>
     </row>
@@ -16487,8 +23593,8 @@
       <c r="A586" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="B586" s="2"/>
-      <c r="C586" s="3"/>
+      <c r="B586" s="1"/>
+      <c r="C586" s="2"/>
     </row>
     <row r="587" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A587" s="7" t="s">
@@ -16777,8 +23883,8 @@
       <c r="A614" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B614" s="2"/>
-      <c r="C614" s="3"/>
+      <c r="B614" s="1"/>
+      <c r="C614" s="2"/>
     </row>
     <row r="615" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A615" s="7" t="s">
@@ -16933,13 +24039,13 @@
     <row r="629" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="630" spans="1:3" ht="20.100000000000001" customHeight="1"/>
     <row r="631" spans="1:3" ht="20.100000000000001" customHeight="1">
-      <c r="A631" s="1" t="s">
+      <c r="A631" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B631" s="1">
-        <v>0</v>
-      </c>
-      <c r="C631" s="1">
+      <c r="B631" s="3">
+        <v>0</v>
+      </c>
+      <c r="C631" s="3">
         <v>0</v>
       </c>
     </row>
@@ -16947,8 +24053,8 @@
       <c r="A632" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="B632" s="2"/>
-      <c r="C632" s="3"/>
+      <c r="B632" s="1"/>
+      <c r="C632" s="2"/>
     </row>
     <row r="633" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A633" s="7" t="s">
@@ -17204,8 +24310,8 @@
       <c r="A657" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B657" s="2"/>
-      <c r="C657" s="3"/>
+      <c r="B657" s="1"/>
+      <c r="C657" s="2"/>
     </row>
     <row r="658" spans="1:3">
       <c r="A658" s="7" t="s">
@@ -17362,13 +24468,13 @@
       </c>
     </row>
     <row r="672" spans="1:3">
-      <c r="A672" s="1" t="s">
+      <c r="A672" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B672" s="1">
-        <v>0</v>
-      </c>
-      <c r="C672" s="1">
+      <c r="B672" s="3">
+        <v>0</v>
+      </c>
+      <c r="C672" s="3">
         <v>0</v>
       </c>
     </row>
@@ -17410,20 +24516,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C675"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="7" t="s">
@@ -17716,8 +24822,8 @@
       <c r="A29" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="7" t="s">
@@ -17879,8 +24985,8 @@
       <c r="A46" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="6"/>
     </row>
     <row r="47" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A47" s="7" t="s">
@@ -18173,8 +25279,8 @@
       <c r="A74" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="6"/>
     </row>
     <row r="75" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A75" s="7" t="s">
@@ -18336,8 +25442,8 @@
       <c r="A91" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="6"/>
     </row>
     <row r="92" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A92" s="7" t="s">
@@ -18641,8 +25747,8 @@
       <c r="A120" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B120" s="16"/>
-      <c r="C120" s="16"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="6"/>
     </row>
     <row r="121" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A121" s="7" t="s">
@@ -18804,8 +25910,8 @@
       <c r="A137" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="B137" s="16"/>
-      <c r="C137" s="16"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="6"/>
     </row>
     <row r="138" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A138" s="7" t="s">
@@ -19098,8 +26204,8 @@
       <c r="A165" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B165" s="16"/>
-      <c r="C165" s="16"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="6"/>
     </row>
     <row r="166" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A166" s="7" t="s">
@@ -19261,8 +26367,8 @@
       <c r="A182" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="B182" s="16"/>
-      <c r="C182" s="16"/>
+      <c r="B182" s="5"/>
+      <c r="C182" s="6"/>
     </row>
     <row r="183" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A183" s="7" t="s">
@@ -19555,8 +26661,8 @@
       <c r="A210" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B210" s="16"/>
-      <c r="C210" s="16"/>
+      <c r="B210" s="5"/>
+      <c r="C210" s="6"/>
     </row>
     <row r="211" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A211" s="7" t="s">
@@ -19718,8 +26824,8 @@
       <c r="A227" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="B227" s="16"/>
-      <c r="C227" s="16"/>
+      <c r="B227" s="5"/>
+      <c r="C227" s="6"/>
     </row>
     <row r="228" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A228" s="7" t="s">
@@ -20012,8 +27118,8 @@
       <c r="A255" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B255" s="16"/>
-      <c r="C255" s="16"/>
+      <c r="B255" s="5"/>
+      <c r="C255" s="6"/>
     </row>
     <row r="256" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A256" s="7" t="s">
@@ -20175,8 +27281,8 @@
       <c r="A272" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="B272" s="16"/>
-      <c r="C272" s="16"/>
+      <c r="B272" s="5"/>
+      <c r="C272" s="6"/>
     </row>
     <row r="273" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A273" s="7" t="s">
@@ -20469,8 +27575,8 @@
       <c r="A300" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B300" s="16"/>
-      <c r="C300" s="16"/>
+      <c r="B300" s="5"/>
+      <c r="C300" s="6"/>
     </row>
     <row r="301" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A301" s="7" t="s">
@@ -20632,8 +27738,8 @@
       <c r="A317" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="B317" s="16"/>
-      <c r="C317" s="16"/>
+      <c r="B317" s="5"/>
+      <c r="C317" s="6"/>
     </row>
     <row r="318" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A318" s="7" t="s">
@@ -20926,8 +28032,8 @@
       <c r="A345" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B345" s="16"/>
-      <c r="C345" s="16"/>
+      <c r="B345" s="5"/>
+      <c r="C345" s="6"/>
     </row>
     <row r="346" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A346" s="7" t="s">
@@ -21089,8 +28195,8 @@
       <c r="A362" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="B362" s="16"/>
-      <c r="C362" s="16"/>
+      <c r="B362" s="5"/>
+      <c r="C362" s="6"/>
     </row>
     <row r="363" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A363" s="7" t="s">
@@ -21394,8 +28500,8 @@
       <c r="A391" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B391" s="16"/>
-      <c r="C391" s="16"/>
+      <c r="B391" s="5"/>
+      <c r="C391" s="6"/>
     </row>
     <row r="392" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A392" s="7" t="s">
@@ -21557,8 +28663,8 @@
       <c r="A408" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="B408" s="16"/>
-      <c r="C408" s="16"/>
+      <c r="B408" s="5"/>
+      <c r="C408" s="6"/>
     </row>
     <row r="409" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A409" s="7" t="s">
@@ -21851,8 +28957,8 @@
       <c r="A436" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B436" s="16"/>
-      <c r="C436" s="16"/>
+      <c r="B436" s="5"/>
+      <c r="C436" s="6"/>
     </row>
     <row r="437" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A437" s="7" t="s">
@@ -22014,8 +29120,8 @@
       <c r="A453" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="B453" s="16"/>
-      <c r="C453" s="16"/>
+      <c r="B453" s="5"/>
+      <c r="C453" s="6"/>
     </row>
     <row r="454" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A454" s="7" t="s">
@@ -22308,8 +29414,8 @@
       <c r="A481" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B481" s="16"/>
-      <c r="C481" s="16"/>
+      <c r="B481" s="5"/>
+      <c r="C481" s="6"/>
     </row>
     <row r="482" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A482" s="7" t="s">
@@ -22471,8 +29577,8 @@
       <c r="A498" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="B498" s="16"/>
-      <c r="C498" s="16"/>
+      <c r="B498" s="5"/>
+      <c r="C498" s="6"/>
     </row>
     <row r="499" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A499" s="7" t="s">
@@ -22765,8 +29871,8 @@
       <c r="A526" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B526" s="16"/>
-      <c r="C526" s="16"/>
+      <c r="B526" s="5"/>
+      <c r="C526" s="6"/>
     </row>
     <row r="527" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A527" s="7" t="s">
@@ -22928,8 +30034,8 @@
       <c r="A543" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="B543" s="16"/>
-      <c r="C543" s="16"/>
+      <c r="B543" s="5"/>
+      <c r="C543" s="6"/>
     </row>
     <row r="544" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A544" s="7" t="s">
@@ -23222,8 +30328,8 @@
       <c r="A571" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B571" s="16"/>
-      <c r="C571" s="16"/>
+      <c r="B571" s="5"/>
+      <c r="C571" s="6"/>
     </row>
     <row r="572" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A572" s="7" t="s">
@@ -23385,8 +30491,8 @@
       <c r="A588" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="B588" s="16"/>
-      <c r="C588" s="16"/>
+      <c r="B588" s="5"/>
+      <c r="C588" s="6"/>
     </row>
     <row r="589" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A589" s="7" t="s">
@@ -23679,8 +30785,8 @@
       <c r="A616" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B616" s="16"/>
-      <c r="C616" s="16"/>
+      <c r="B616" s="5"/>
+      <c r="C616" s="6"/>
     </row>
     <row r="617" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A617" s="7" t="s">
@@ -23842,8 +30948,8 @@
       <c r="A633" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="B633" s="16"/>
-      <c r="C633" s="16"/>
+      <c r="B633" s="5"/>
+      <c r="C633" s="6"/>
     </row>
     <row r="634" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A634" s="7" t="s">
@@ -24136,8 +31242,8 @@
       <c r="A661" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B661" s="16"/>
-      <c r="C661" s="16"/>
+      <c r="B661" s="5"/>
+      <c r="C661" s="6"/>
     </row>
     <row r="662" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A662" s="7" t="s">
@@ -24331,12 +31437,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C673"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1">
@@ -31211,8 +38317,8 @@
     <mergeCell ref="A224:C224"/>
     <mergeCell ref="A342:C342"/>
     <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A495:C495"/>
     <mergeCell ref="A451:C451"/>
-    <mergeCell ref="A495:C495"/>
     <mergeCell ref="A180:C180"/>
     <mergeCell ref="A434:C434"/>
     <mergeCell ref="A586:C586"/>
@@ -31230,12 +38336,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C677"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1">
@@ -38139,7 +45245,7 @@
   <mergeCells count="30">
     <mergeCell ref="A663:C663"/>
     <mergeCell ref="A166:C166"/>
-    <mergeCell ref="A634:C634"/>
+    <mergeCell ref="A498:C498"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A589:C589"/>
     <mergeCell ref="A408:C408"/>
@@ -38148,7 +45254,7 @@
     <mergeCell ref="A346:C346"/>
     <mergeCell ref="A256:C256"/>
     <mergeCell ref="A363:C363"/>
-    <mergeCell ref="A498:C498"/>
+    <mergeCell ref="A634:C634"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A436:C436"/>
     <mergeCell ref="A318:C318"/>
@@ -38173,12 +45279,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C673"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1"/>
@@ -45020,7 +52126,6 @@
     <mergeCell ref="A227:C227"/>
     <mergeCell ref="A345:C345"/>
     <mergeCell ref="A631:C631"/>
-    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A479:C479"/>
     <mergeCell ref="A451:C451"/>
     <mergeCell ref="A165:C165"/>
@@ -45028,10 +52133,8 @@
     <mergeCell ref="A541:C541"/>
     <mergeCell ref="A362:C362"/>
     <mergeCell ref="A569:C569"/>
-    <mergeCell ref="A92:C92"/>
     <mergeCell ref="A182:C182"/>
     <mergeCell ref="A300:C300"/>
-    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A614:C614"/>
     <mergeCell ref="A496:C496"/>
     <mergeCell ref="A3:C3"/>
@@ -45041,6 +52144,9 @@
     <mergeCell ref="A272:C272"/>
     <mergeCell ref="A210:C210"/>
     <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A137:C137"/>
     <mergeCell ref="A255:C255"/>
     <mergeCell ref="A75:C75"/>
@@ -45052,12 +52158,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C672"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1"/>
@@ -51920,12 +59026,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C673"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1">
@@ -58819,12 +65925,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C678"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="3" width="24" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40" style="3" customWidth="1"/>
+    <col min="2" max="3" width="24" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1"/>
